--- a/compare/output/dscale_GreenElec_downscaled_SSP126.xlsx
+++ b/compare/output/dscale_GreenElec_downscaled_SSP126.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1481.741498</v>
+        <v>1481.977213</v>
       </c>
       <c r="F2" t="n">
-        <v>3701.893311</v>
+        <v>3703.312451</v>
       </c>
       <c r="G2" t="n">
-        <v>8627.42093</v>
+        <v>8633.911475000001</v>
       </c>
       <c r="H2" t="n">
-        <v>16725.711162</v>
+        <v>16750.695051</v>
       </c>
       <c r="I2" t="n">
-        <v>29387.919182</v>
+        <v>29496.005204</v>
       </c>
       <c r="J2" t="n">
         <v>37771.962959</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>125.139973</v>
+        <v>125.084144</v>
       </c>
       <c r="F3" t="n">
-        <v>277.888659</v>
+        <v>277.570648</v>
       </c>
       <c r="G3" t="n">
-        <v>610.748766</v>
+        <v>609.310403</v>
       </c>
       <c r="H3" t="n">
-        <v>1175.543727</v>
+        <v>1169.880188</v>
       </c>
       <c r="I3" t="n">
-        <v>2114.363301</v>
+        <v>2088.819265</v>
       </c>
       <c r="J3" t="n">
         <v>6623.54983</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>149.258609</v>
+        <v>148.995324</v>
       </c>
       <c r="F4" t="n">
-        <v>286.045624</v>
+        <v>284.79238</v>
       </c>
       <c r="G4" t="n">
-        <v>533.749958</v>
+        <v>529.109148</v>
       </c>
       <c r="H4" t="n">
-        <v>918.28452</v>
+        <v>902.4824599999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1558.55206</v>
+        <v>1494.328431</v>
       </c>
       <c r="J4" t="n">
         <v>9313.631498999999</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>79.020443</v>
+        <v>78.447289</v>
       </c>
       <c r="F5" t="n">
-        <v>224.158549</v>
+        <v>220.019036</v>
       </c>
       <c r="G5" t="n">
-        <v>663.527303</v>
+        <v>638.662552</v>
       </c>
       <c r="H5" t="n">
-        <v>1641.107998</v>
+        <v>1521.11303</v>
       </c>
       <c r="I5" t="n">
-        <v>3820.928573</v>
+        <v>3216.895048</v>
       </c>
       <c r="J5" t="n">
         <v>78773.213219</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>37115.821034</v>
+        <v>37122.870226</v>
       </c>
       <c r="F6" t="n">
-        <v>90242.730428</v>
+        <v>90284.516554</v>
       </c>
       <c r="G6" t="n">
-        <v>187365.00463</v>
+        <v>187540.506824</v>
       </c>
       <c r="H6" t="n">
-        <v>330482.941276</v>
+        <v>331112.551995</v>
       </c>
       <c r="I6" t="n">
-        <v>550742.7184210001</v>
+        <v>553365.089436</v>
       </c>
       <c r="J6" t="n">
         <v>625270.646957</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29564.302842</v>
+        <v>29570.720279</v>
       </c>
       <c r="F7" t="n">
-        <v>74679.098881</v>
+        <v>74718.601757</v>
       </c>
       <c r="G7" t="n">
-        <v>185514.585903</v>
+        <v>185706.733478</v>
       </c>
       <c r="H7" t="n">
-        <v>395115.388138</v>
+        <v>395918.311085</v>
       </c>
       <c r="I7" t="n">
-        <v>756887.943153</v>
+        <v>760632.116411</v>
       </c>
       <c r="J7" t="n">
         <v>930808.429827</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3383.87281</v>
+        <v>3382.579557</v>
       </c>
       <c r="F8" t="n">
-        <v>8209.117214</v>
+        <v>8200.953604</v>
       </c>
       <c r="G8" t="n">
-        <v>18776.967953</v>
+        <v>18738.457229</v>
       </c>
       <c r="H8" t="n">
-        <v>36244.116237</v>
+        <v>36092.824436</v>
       </c>
       <c r="I8" t="n">
-        <v>64554.000759</v>
+        <v>63882.06091</v>
       </c>
       <c r="J8" t="n">
         <v>184466.861756</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2421.349177</v>
+        <v>2419.933043</v>
       </c>
       <c r="F9" t="n">
-        <v>4524.940691</v>
+        <v>4518.342252</v>
       </c>
       <c r="G9" t="n">
-        <v>7852.526286</v>
+        <v>7829.954309</v>
       </c>
       <c r="H9" t="n">
-        <v>12142.496645</v>
+        <v>12073.894098</v>
       </c>
       <c r="I9" t="n">
-        <v>18159.47199</v>
+        <v>17910.877285</v>
       </c>
       <c r="J9" t="n">
         <v>50704.411686</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1075.822733</v>
+        <v>1073.847351</v>
       </c>
       <c r="F10" t="n">
-        <v>2449.216824</v>
+        <v>2437.845543</v>
       </c>
       <c r="G10" t="n">
-        <v>5030.800431</v>
+        <v>4984.066058</v>
       </c>
       <c r="H10" t="n">
-        <v>9082.319267999999</v>
+        <v>8915.103756</v>
       </c>
       <c r="I10" t="n">
-        <v>15893.601019</v>
+        <v>15195.093179</v>
       </c>
       <c r="J10" t="n">
         <v>102503.306127</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29970.261953</v>
+        <v>29964.286902</v>
       </c>
       <c r="F11" t="n">
-        <v>70382.411439</v>
+        <v>70345.457129</v>
       </c>
       <c r="G11" t="n">
-        <v>156648.97563</v>
+        <v>156478.106365</v>
       </c>
       <c r="H11" t="n">
-        <v>299803.448593</v>
+        <v>299131.536533</v>
       </c>
       <c r="I11" t="n">
-        <v>526225.090889</v>
+        <v>523252.914462</v>
       </c>
       <c r="J11" t="n">
         <v>1155986.589414</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1574.068328</v>
+        <v>1574.161116</v>
       </c>
       <c r="F12" t="n">
-        <v>3861.86061</v>
+        <v>3862.337073</v>
       </c>
       <c r="G12" t="n">
-        <v>9180.700696</v>
+        <v>9182.582396</v>
       </c>
       <c r="H12" t="n">
-        <v>18548.988121</v>
+        <v>18555.346598</v>
       </c>
       <c r="I12" t="n">
-        <v>33807.803192</v>
+        <v>33831.593346</v>
       </c>
       <c r="J12" t="n">
         <v>56754.831539</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12301.917599</v>
+        <v>12299.674558</v>
       </c>
       <c r="F13" t="n">
-        <v>29900.05207</v>
+        <v>29885.665871</v>
       </c>
       <c r="G13" t="n">
-        <v>67149.752114</v>
+        <v>67083.360363</v>
       </c>
       <c r="H13" t="n">
-        <v>130773.178915</v>
+        <v>130509.78537</v>
       </c>
       <c r="I13" t="n">
-        <v>239035.242061</v>
+        <v>237821.841622</v>
       </c>
       <c r="J13" t="n">
         <v>565786.019787</v>
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>800.332691</v>
+        <v>800.117604</v>
       </c>
       <c r="F14" t="n">
-        <v>2055.692118</v>
+        <v>2054.233658</v>
       </c>
       <c r="G14" t="n">
-        <v>5350.836906</v>
+        <v>5342.544371</v>
       </c>
       <c r="H14" t="n">
-        <v>9943.123764</v>
+        <v>9908.630084</v>
       </c>
       <c r="I14" t="n">
-        <v>16808.857748</v>
+        <v>16645.171748</v>
       </c>
       <c r="J14" t="n">
         <v>564770.492319</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>56957.726405</v>
+        <v>56958.1015</v>
       </c>
       <c r="F15" t="n">
-        <v>160506.339393</v>
+        <v>160508.608777</v>
       </c>
       <c r="G15" t="n">
-        <v>435782.032314</v>
+        <v>435793.237768</v>
       </c>
       <c r="H15" t="n">
-        <v>823455.320329</v>
+        <v>823497.508442</v>
       </c>
       <c r="I15" t="n">
-        <v>1387547.613437</v>
+        <v>1387736.719731</v>
       </c>
       <c r="J15" t="n">
         <v>1396142.193569</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>29.226925</v>
+        <v>28.972118</v>
       </c>
       <c r="F16" t="n">
-        <v>65.643356</v>
+        <v>64.32665799999999</v>
       </c>
       <c r="G16" t="n">
-        <v>145.47966</v>
+        <v>140.095295</v>
       </c>
       <c r="H16" t="n">
-        <v>245.658105</v>
+        <v>228.440569</v>
       </c>
       <c r="I16" t="n">
-        <v>436.924034</v>
+        <v>368.90356</v>
       </c>
       <c r="J16" t="n">
         <v>200322.445219</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>15887.986739</v>
+        <v>15888.135792</v>
       </c>
       <c r="F17" t="n">
-        <v>41774.028844</v>
+        <v>41774.959568</v>
       </c>
       <c r="G17" t="n">
-        <v>107333.860949</v>
+        <v>107338.621538</v>
       </c>
       <c r="H17" t="n">
-        <v>193070.451867</v>
+        <v>193088.60655</v>
       </c>
       <c r="I17" t="n">
-        <v>312559.373328</v>
+        <v>312640.023334</v>
       </c>
       <c r="J17" t="n">
         <v>183249.913029</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1992.667175</v>
+        <v>1992.612922</v>
       </c>
       <c r="F18" t="n">
-        <v>5373.380649</v>
+        <v>5372.955699</v>
       </c>
       <c r="G18" t="n">
-        <v>13369.974171</v>
+        <v>13367.685028</v>
       </c>
       <c r="H18" t="n">
-        <v>23301.855635</v>
+        <v>23293.224055</v>
       </c>
       <c r="I18" t="n">
-        <v>37250.690153</v>
+        <v>37212.640327</v>
       </c>
       <c r="J18" t="n">
         <v>176274.973563</v>
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>18790.086951</v>
+        <v>18786.16229</v>
       </c>
       <c r="F19" t="n">
-        <v>27199.739187</v>
+        <v>27185.260398</v>
       </c>
       <c r="G19" t="n">
-        <v>40988.638563</v>
+        <v>40943.954142</v>
       </c>
       <c r="H19" t="n">
-        <v>66451.13579499999</v>
+        <v>66302.640084</v>
       </c>
       <c r="I19" t="n">
-        <v>101996.673153</v>
+        <v>101419.568106</v>
       </c>
       <c r="J19" t="n">
         <v>550230.02205</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>14.583154</v>
+        <v>13.452693</v>
       </c>
       <c r="F20" t="n">
-        <v>27.248452</v>
+        <v>23.449243</v>
       </c>
       <c r="G20" t="n">
-        <v>61.16727</v>
+        <v>49.577002</v>
       </c>
       <c r="H20" t="n">
-        <v>164.518157</v>
+        <v>126.754658</v>
       </c>
       <c r="I20" t="n">
-        <v>534.100264</v>
+        <v>394.664286</v>
       </c>
       <c r="J20" t="n">
         <v>89646.189402</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>349.756232</v>
+        <v>349.653484</v>
       </c>
       <c r="F21" t="n">
-        <v>408.256353</v>
+        <v>407.956198</v>
       </c>
       <c r="G21" t="n">
-        <v>540.315143</v>
+        <v>539.510039</v>
       </c>
       <c r="H21" t="n">
-        <v>828.932182</v>
+        <v>826.409272</v>
       </c>
       <c r="I21" t="n">
-        <v>1256.228017</v>
+        <v>1246.570169</v>
       </c>
       <c r="J21" t="n">
         <v>8552.885644</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>61254.697193</v>
+        <v>61259.102901</v>
       </c>
       <c r="F22" t="n">
-        <v>89269.689513</v>
+        <v>89285.99486799999</v>
       </c>
       <c r="G22" t="n">
-        <v>135368.285416</v>
+        <v>135417.264454</v>
       </c>
       <c r="H22" t="n">
-        <v>218678.066424</v>
+        <v>218832.305786</v>
       </c>
       <c r="I22" t="n">
-        <v>330555.992741</v>
+        <v>331119.076744</v>
       </c>
       <c r="J22" t="n">
         <v>112063.380863</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2650.0463</v>
+        <v>2649.739044</v>
       </c>
       <c r="F23" t="n">
-        <v>3999.853943</v>
+        <v>3998.663311</v>
       </c>
       <c r="G23" t="n">
-        <v>6472.23976</v>
+        <v>6468.221987</v>
       </c>
       <c r="H23" t="n">
-        <v>11448.44611</v>
+        <v>11433.524448</v>
       </c>
       <c r="I23" t="n">
-        <v>19066.321315</v>
+        <v>19001.733602</v>
       </c>
       <c r="J23" t="n">
         <v>79700.111745</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5392.74138</v>
+        <v>5392.571557</v>
       </c>
       <c r="F24" t="n">
-        <v>7176.690231</v>
+        <v>7176.116163</v>
       </c>
       <c r="G24" t="n">
-        <v>10479.522291</v>
+        <v>10477.703064</v>
       </c>
       <c r="H24" t="n">
-        <v>16624.703212</v>
+        <v>16618.293739</v>
       </c>
       <c r="I24" t="n">
-        <v>24540.332049</v>
+        <v>24514.362827</v>
       </c>
       <c r="J24" t="n">
         <v>52554.711856</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1291.491048</v>
+        <v>1291.38648</v>
       </c>
       <c r="F25" t="n">
-        <v>1598.924703</v>
+        <v>1598.600009</v>
       </c>
       <c r="G25" t="n">
-        <v>2261.946566</v>
+        <v>2260.990876</v>
       </c>
       <c r="H25" t="n">
-        <v>3636.711223</v>
+        <v>3633.453693</v>
       </c>
       <c r="I25" t="n">
-        <v>5505.550701</v>
+        <v>5492.589082</v>
       </c>
       <c r="J25" t="n">
         <v>16862.307256</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7816.861114</v>
+        <v>7814.0816</v>
       </c>
       <c r="F26" t="n">
-        <v>11104.888071</v>
+        <v>11094.842951</v>
       </c>
       <c r="G26" t="n">
-        <v>15933.252674</v>
+        <v>15904.030363</v>
       </c>
       <c r="H26" t="n">
-        <v>24407.787833</v>
+        <v>24317.360564</v>
       </c>
       <c r="I26" t="n">
-        <v>35910.718639</v>
+        <v>35580.203645</v>
       </c>
       <c r="J26" t="n">
         <v>271176.907575</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>46589.263038</v>
+        <v>46591.794281</v>
       </c>
       <c r="F27" t="n">
-        <v>66559.634857</v>
+        <v>66568.81872700001</v>
       </c>
       <c r="G27" t="n">
-        <v>98202.99386800001</v>
+        <v>98229.649573</v>
       </c>
       <c r="H27" t="n">
-        <v>158563.468092</v>
+        <v>158646.209847</v>
       </c>
       <c r="I27" t="n">
-        <v>242213.995075</v>
+        <v>242513.754069</v>
       </c>
       <c r="J27" t="n">
         <v>163084.449261</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>18198.377891</v>
+        <v>18199.959968</v>
       </c>
       <c r="F28" t="n">
-        <v>23617.808105</v>
+        <v>23623.031545</v>
       </c>
       <c r="G28" t="n">
-        <v>39656.477188</v>
+        <v>39673.937241</v>
       </c>
       <c r="H28" t="n">
-        <v>77278.857582</v>
+        <v>77345.67451899999</v>
       </c>
       <c r="I28" t="n">
-        <v>141107.392655</v>
+        <v>141404.782079</v>
       </c>
       <c r="J28" t="n">
         <v>11083.511959</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>22.338784</v>
+        <v>22.295872</v>
       </c>
       <c r="F29" t="n">
-        <v>33.923525</v>
+        <v>33.754009</v>
       </c>
       <c r="G29" t="n">
-        <v>55.575911</v>
+        <v>54.988731</v>
       </c>
       <c r="H29" t="n">
-        <v>96.361941</v>
+        <v>94.225701</v>
       </c>
       <c r="I29" t="n">
-        <v>178.906577</v>
+        <v>168.977924</v>
       </c>
       <c r="J29" t="n">
         <v>26624.801793</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>411.749953</v>
+        <v>411.707776</v>
       </c>
       <c r="F30" t="n">
-        <v>587.528103</v>
+        <v>587.371764</v>
       </c>
       <c r="G30" t="n">
-        <v>897.75271</v>
+        <v>897.2343069999999</v>
       </c>
       <c r="H30" t="n">
-        <v>1476.087831</v>
+        <v>1474.226576</v>
       </c>
       <c r="I30" t="n">
-        <v>2486.092498</v>
+        <v>2477.660427</v>
       </c>
       <c r="J30" t="n">
         <v>26113.574333</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>770.6890990000001</v>
+        <v>770.703543</v>
       </c>
       <c r="F31" t="n">
-        <v>1226.89891</v>
+        <v>1226.950347</v>
       </c>
       <c r="G31" t="n">
-        <v>1996.134439</v>
+        <v>1996.256561</v>
       </c>
       <c r="H31" t="n">
-        <v>3392.045488</v>
+        <v>3392.335912</v>
       </c>
       <c r="I31" t="n">
-        <v>5864.934857</v>
+        <v>5865.863616</v>
       </c>
       <c r="J31" t="n">
         <v>7916.200458</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5403.42982</v>
+        <v>5403.49634</v>
       </c>
       <c r="F32" t="n">
-        <v>7467.496661</v>
+        <v>7467.699606</v>
       </c>
       <c r="G32" t="n">
-        <v>11130.011534</v>
+        <v>11130.372577</v>
       </c>
       <c r="H32" t="n">
-        <v>18020.222505</v>
+        <v>18020.695739</v>
       </c>
       <c r="I32" t="n">
-        <v>30624.9744</v>
+        <v>30624.904501</v>
       </c>
       <c r="J32" t="n">
         <v>54673.968435</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>16295.279162</v>
+        <v>16295.632378</v>
       </c>
       <c r="F33" t="n">
-        <v>24407.205136</v>
+        <v>24408.440886</v>
       </c>
       <c r="G33" t="n">
-        <v>39218.265846</v>
+        <v>39221.41643</v>
       </c>
       <c r="H33" t="n">
-        <v>66234.611107</v>
+        <v>66243.065357</v>
       </c>
       <c r="I33" t="n">
-        <v>113365.777745</v>
+        <v>113396.896468</v>
       </c>
       <c r="J33" t="n">
         <v>114211.187823</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>33149.934486</v>
+        <v>33150.956103</v>
       </c>
       <c r="F34" t="n">
-        <v>87196.563171</v>
+        <v>87202.962025</v>
       </c>
       <c r="G34" t="n">
-        <v>237907.491737</v>
+        <v>237937.436285</v>
       </c>
       <c r="H34" t="n">
-        <v>580944.196554</v>
+        <v>581072.198952</v>
       </c>
       <c r="I34" t="n">
-        <v>1247731.271801</v>
+        <v>1248374.062898</v>
       </c>
       <c r="J34" t="n">
         <v>557986.321353</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4071.996302</v>
+        <v>4072.069321</v>
       </c>
       <c r="F35" t="n">
-        <v>7499.824901</v>
+        <v>7500.107742</v>
       </c>
       <c r="G35" t="n">
-        <v>14414.125286</v>
+        <v>14414.796216</v>
       </c>
       <c r="H35" t="n">
-        <v>26709.10623</v>
+        <v>26710.388418</v>
       </c>
       <c r="I35" t="n">
-        <v>46615.587153</v>
+        <v>46618.281846</v>
       </c>
       <c r="J35" t="n">
         <v>70181.742304</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>82.759022</v>
+        <v>82.74587</v>
       </c>
       <c r="F36" t="n">
-        <v>122.760723</v>
+        <v>122.707247</v>
       </c>
       <c r="G36" t="n">
-        <v>172.997056</v>
+        <v>172.835602</v>
       </c>
       <c r="H36" t="n">
-        <v>248.537267</v>
+        <v>248.048217</v>
       </c>
       <c r="I36" t="n">
-        <v>365.02494</v>
+        <v>363.15525</v>
       </c>
       <c r="J36" t="n">
         <v>4648.58375</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4535.707652</v>
+        <v>4535.718824</v>
       </c>
       <c r="F37" t="n">
-        <v>6003.562323</v>
+        <v>6003.582309</v>
       </c>
       <c r="G37" t="n">
-        <v>8420.930651999999</v>
+        <v>8420.816293</v>
       </c>
       <c r="H37" t="n">
-        <v>12596.175212</v>
+        <v>12595.401341</v>
       </c>
       <c r="I37" t="n">
-        <v>19372.232472</v>
+        <v>19368.261313</v>
       </c>
       <c r="J37" t="n">
         <v>38416.949116</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>21687.288758</v>
+        <v>21687.854194</v>
       </c>
       <c r="F38" t="n">
-        <v>33076.089583</v>
+        <v>33078.146078</v>
       </c>
       <c r="G38" t="n">
-        <v>52276.579516</v>
+        <v>52282.097463</v>
       </c>
       <c r="H38" t="n">
-        <v>88320.778376</v>
+        <v>88336.89930799999</v>
       </c>
       <c r="I38" t="n">
-        <v>154024.266727</v>
+        <v>154089.307448</v>
       </c>
       <c r="J38" t="n">
         <v>100723.278712</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1738.890578</v>
+        <v>1738.917047</v>
       </c>
       <c r="F39" t="n">
-        <v>2521.879317</v>
+        <v>2521.964801</v>
       </c>
       <c r="G39" t="n">
-        <v>4016.768603</v>
+        <v>4016.945697</v>
       </c>
       <c r="H39" t="n">
-        <v>6871.4943</v>
+        <v>6871.814877</v>
       </c>
       <c r="I39" t="n">
-        <v>12167.18977</v>
+        <v>12167.715806</v>
       </c>
       <c r="J39" t="n">
         <v>21105.300721</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>265.694354</v>
+        <v>265.696992</v>
       </c>
       <c r="F40" t="n">
-        <v>405.452737</v>
+        <v>405.46043</v>
       </c>
       <c r="G40" t="n">
-        <v>651.236767</v>
+        <v>651.244511</v>
       </c>
       <c r="H40" t="n">
-        <v>1083.025258</v>
+        <v>1083.003907</v>
       </c>
       <c r="I40" t="n">
-        <v>1847.022778</v>
+        <v>1846.791587</v>
       </c>
       <c r="J40" t="n">
         <v>3791.626964</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>312.707818</v>
+        <v>312.700928</v>
       </c>
       <c r="F41" t="n">
-        <v>524.89373</v>
+        <v>524.856687</v>
       </c>
       <c r="G41" t="n">
-        <v>865.68459</v>
+        <v>865.526552</v>
       </c>
       <c r="H41" t="n">
-        <v>1459.438582</v>
+        <v>1458.797362</v>
       </c>
       <c r="I41" t="n">
-        <v>2435.205525</v>
+        <v>2432.197341</v>
       </c>
       <c r="J41" t="n">
         <v>11532.027699</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1732.282975</v>
+        <v>1732.122562</v>
       </c>
       <c r="F42" t="n">
-        <v>2395.731789</v>
+        <v>2395.162583</v>
       </c>
       <c r="G42" t="n">
-        <v>3331.772816</v>
+        <v>3330.120662</v>
       </c>
       <c r="H42" t="n">
-        <v>4862.237313</v>
+        <v>4857.22311</v>
       </c>
       <c r="I42" t="n">
-        <v>7409.543538</v>
+        <v>7389.764944</v>
       </c>
       <c r="J42" t="n">
         <v>56029.416809</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>774.605084</v>
+        <v>774.624426</v>
       </c>
       <c r="F43" t="n">
-        <v>1600.826888</v>
+        <v>1600.918398</v>
       </c>
       <c r="G43" t="n">
-        <v>3245.572406</v>
+        <v>3245.867618</v>
       </c>
       <c r="H43" t="n">
-        <v>6382.874241</v>
+        <v>6383.806842</v>
       </c>
       <c r="I43" t="n">
-        <v>12191.380079</v>
+        <v>12195.238877</v>
       </c>
       <c r="J43" t="n">
         <v>12255.804687</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4446.591101</v>
+        <v>4446.655742</v>
       </c>
       <c r="F44" t="n">
-        <v>7518.251372</v>
+        <v>7518.477969</v>
       </c>
       <c r="G44" t="n">
-        <v>12774.387395</v>
+        <v>12774.839092</v>
       </c>
       <c r="H44" t="n">
-        <v>22882.192579</v>
+        <v>22882.825307</v>
       </c>
       <c r="I44" t="n">
-        <v>42078.615617</v>
+        <v>42078.321791</v>
       </c>
       <c r="J44" t="n">
         <v>80227.17035</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>534.0783750000001</v>
+        <v>534.06513</v>
       </c>
       <c r="F45" t="n">
-        <v>827.477031</v>
+        <v>827.415995</v>
       </c>
       <c r="G45" t="n">
-        <v>1319.219632</v>
+        <v>1318.974098</v>
       </c>
       <c r="H45" t="n">
-        <v>2187.717037</v>
+        <v>2186.745216</v>
       </c>
       <c r="I45" t="n">
-        <v>3642.698712</v>
+        <v>3638.141402</v>
       </c>
       <c r="J45" t="n">
         <v>17575.367677</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>14.900685</v>
+        <v>14.868034</v>
       </c>
       <c r="F46" t="n">
-        <v>26.097091</v>
+        <v>25.941899</v>
       </c>
       <c r="G46" t="n">
-        <v>47.871156</v>
+        <v>47.252481</v>
       </c>
       <c r="H46" t="n">
-        <v>90.360246</v>
+        <v>87.882288</v>
       </c>
       <c r="I46" t="n">
-        <v>181.912236</v>
+        <v>169.516236</v>
       </c>
       <c r="J46" t="n">
         <v>35465.124582</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>23883.761546</v>
+        <v>23882.030705</v>
       </c>
       <c r="F47" t="n">
-        <v>41438.887961</v>
+        <v>41430.151004</v>
       </c>
       <c r="G47" t="n">
-        <v>70139.315301</v>
+        <v>70105.20679700001</v>
       </c>
       <c r="H47" t="n">
-        <v>121717.313506</v>
+        <v>121584.265339</v>
       </c>
       <c r="I47" t="n">
-        <v>214086.855848</v>
+        <v>213445.255754</v>
       </c>
       <c r="J47" t="n">
         <v>2100915.079004</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>285.754569</v>
+        <v>285.662789</v>
       </c>
       <c r="F48" t="n">
-        <v>448.590825</v>
+        <v>448.200985</v>
       </c>
       <c r="G48" t="n">
-        <v>730.493355</v>
+        <v>729.103339</v>
       </c>
       <c r="H48" t="n">
-        <v>1212.564521</v>
+        <v>1207.576525</v>
       </c>
       <c r="I48" t="n">
-        <v>2039.54405</v>
+        <v>2017.276653</v>
       </c>
       <c r="J48" t="n">
         <v>59034.065609</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1053.608735</v>
+        <v>1053.616013</v>
       </c>
       <c r="F49" t="n">
-        <v>1737.877668</v>
+        <v>1737.894061</v>
       </c>
       <c r="G49" t="n">
-        <v>2890.731107</v>
+        <v>2890.70381</v>
       </c>
       <c r="H49" t="n">
-        <v>4888.936995</v>
+        <v>4888.618584</v>
       </c>
       <c r="I49" t="n">
-        <v>8318.169848</v>
+        <v>8316.171060999999</v>
       </c>
       <c r="J49" t="n">
         <v>19016.661054</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>28.172142</v>
+        <v>28.171335</v>
       </c>
       <c r="F50" t="n">
-        <v>41.142535</v>
+        <v>41.139104</v>
       </c>
       <c r="G50" t="n">
-        <v>58.643939</v>
+        <v>58.632341</v>
       </c>
       <c r="H50" t="n">
-        <v>85.434625</v>
+        <v>85.396581</v>
       </c>
       <c r="I50" t="n">
-        <v>127.169243</v>
+        <v>127.016002</v>
       </c>
       <c r="J50" t="n">
         <v>534.515571</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.166237</v>
+        <v>0.083895</v>
       </c>
       <c r="F51" t="n">
-        <v>0.632839</v>
+        <v>0.319392</v>
       </c>
       <c r="G51" t="n">
-        <v>2.039334</v>
+        <v>1.029311</v>
       </c>
       <c r="H51" t="n">
-        <v>6.888733</v>
+        <v>3.477373</v>
       </c>
       <c r="I51" t="n">
-        <v>30.319433</v>
+        <v>15.310972</v>
       </c>
       <c r="J51" t="n">
         <v>38445.900369</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>211.412761</v>
+        <v>211.404181</v>
       </c>
       <c r="F52" t="n">
-        <v>286.973429</v>
+        <v>286.942929</v>
       </c>
       <c r="G52" t="n">
-        <v>404.210182</v>
+        <v>404.114496</v>
       </c>
       <c r="H52" t="n">
-        <v>609.305823</v>
+        <v>608.987435</v>
       </c>
       <c r="I52" t="n">
-        <v>976.785424</v>
+        <v>975.391152</v>
       </c>
       <c r="J52" t="n">
         <v>5293.132098</v>
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>112510.513874</v>
+        <v>112510.460446</v>
       </c>
       <c r="F54" t="n">
-        <v>163039.740206</v>
+        <v>163039.532097</v>
       </c>
       <c r="G54" t="n">
-        <v>273622.206278</v>
+        <v>273621.451849</v>
       </c>
       <c r="H54" t="n">
-        <v>443961.362848</v>
+        <v>443958.73984</v>
       </c>
       <c r="I54" t="n">
-        <v>634674.739334</v>
+        <v>634664.784179</v>
       </c>
       <c r="J54" t="n">
         <v>1430843.505972</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>121043.411726</v>
+        <v>121043.465154</v>
       </c>
       <c r="F55" t="n">
-        <v>163172.674064</v>
+        <v>163172.882173</v>
       </c>
       <c r="G55" t="n">
-        <v>259438.540022</v>
+        <v>259439.294451</v>
       </c>
       <c r="H55" t="n">
-        <v>405401.892952</v>
+        <v>405404.51596</v>
       </c>
       <c r="I55" t="n">
-        <v>564889.051466</v>
+        <v>564899.006621</v>
       </c>
       <c r="J55" t="n">
         <v>91518.19482800001</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.759956</v>
+        <v>0.30963</v>
       </c>
       <c r="F58" t="n">
-        <v>4.01547</v>
+        <v>1.636457</v>
       </c>
       <c r="G58" t="n">
-        <v>14.589612</v>
+        <v>5.948429</v>
       </c>
       <c r="H58" t="n">
-        <v>45.006041</v>
+        <v>18.366195</v>
       </c>
       <c r="I58" t="n">
-        <v>165.099897</v>
+        <v>67.557137</v>
       </c>
       <c r="J58" t="n">
         <v>29632.82316</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.161483</v>
+        <v>0.065793</v>
       </c>
       <c r="F59" t="n">
-        <v>0.940506</v>
+        <v>0.383292</v>
       </c>
       <c r="G59" t="n">
-        <v>3.736761</v>
+        <v>1.52354</v>
       </c>
       <c r="H59" t="n">
-        <v>11.998499</v>
+        <v>4.896382</v>
       </c>
       <c r="I59" t="n">
-        <v>44.713001</v>
+        <v>18.296088</v>
       </c>
       <c r="J59" t="n">
         <v>8068.337043</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.372849</v>
+        <v>0.151911</v>
       </c>
       <c r="F60" t="n">
-        <v>1.532228</v>
+        <v>0.624441</v>
       </c>
       <c r="G60" t="n">
-        <v>4.432674</v>
+        <v>1.807275</v>
       </c>
       <c r="H60" t="n">
-        <v>11.907264</v>
+        <v>4.85915</v>
       </c>
       <c r="I60" t="n">
-        <v>41.052202</v>
+        <v>16.798128</v>
       </c>
       <c r="J60" t="n">
         <v>7227.655741</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>38309.227635</v>
+        <v>38313.787716</v>
       </c>
       <c r="F61" t="n">
-        <v>82080.673047</v>
+        <v>82104.981625</v>
       </c>
       <c r="G61" t="n">
-        <v>144028.330571</v>
+        <v>144113.499971</v>
       </c>
       <c r="H61" t="n">
-        <v>212206.075438</v>
+        <v>212459.908478</v>
       </c>
       <c r="I61" t="n">
-        <v>299493.813884</v>
+        <v>300397.358668</v>
       </c>
       <c r="J61" t="n">
         <v>132439.067305</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2875.538796</v>
+        <v>2870.672036</v>
       </c>
       <c r="F62" t="n">
-        <v>6344.791706</v>
+        <v>6316.528886</v>
       </c>
       <c r="G62" t="n">
-        <v>11229.932281</v>
+        <v>11126.42795</v>
       </c>
       <c r="H62" t="n">
-        <v>16487.034389</v>
+        <v>16178.123043</v>
       </c>
       <c r="I62" t="n">
-        <v>23558.527985</v>
+        <v>22483.225453</v>
       </c>
       <c r="J62" t="n">
         <v>335914.370821</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4805.652422</v>
+        <v>4802.513002</v>
       </c>
       <c r="F63" t="n">
-        <v>10494.918984</v>
+        <v>10477.062617</v>
       </c>
       <c r="G63" t="n">
-        <v>18475.361871</v>
+        <v>18410.769822</v>
       </c>
       <c r="H63" t="n">
-        <v>27700.267558</v>
+        <v>27501.944918</v>
       </c>
       <c r="I63" t="n">
-        <v>40658.718769</v>
+        <v>39924.62805</v>
       </c>
       <c r="J63" t="n">
         <v>280870.076805</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.069466</v>
+        <v>0.028303</v>
       </c>
       <c r="F64" t="n">
-        <v>0.32542</v>
+        <v>0.132621</v>
       </c>
       <c r="G64" t="n">
-        <v>1.090473</v>
+        <v>0.444604</v>
       </c>
       <c r="H64" t="n">
-        <v>3.209565</v>
+        <v>1.309769</v>
       </c>
       <c r="I64" t="n">
-        <v>11.596724</v>
+        <v>4.745257</v>
       </c>
       <c r="J64" t="n">
         <v>2081.503049</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>24278.857257</v>
+        <v>24279.837401</v>
       </c>
       <c r="F65" t="n">
-        <v>56859.088445</v>
+        <v>56864.051857</v>
       </c>
       <c r="G65" t="n">
-        <v>109443.343731</v>
+        <v>109459.621072</v>
       </c>
       <c r="H65" t="n">
-        <v>174219.49124</v>
+        <v>174265.601165</v>
       </c>
       <c r="I65" t="n">
-        <v>262572.177799</v>
+        <v>262725.648241</v>
       </c>
       <c r="J65" t="n">
         <v>326828.991527</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>14341.039289</v>
+        <v>14342.668313</v>
       </c>
       <c r="F66" t="n">
-        <v>33358.976301</v>
+        <v>33368.282986</v>
       </c>
       <c r="G66" t="n">
-        <v>64429.414909</v>
+        <v>64464.727837</v>
       </c>
       <c r="H66" t="n">
-        <v>103554.749193</v>
+        <v>103667.814097</v>
       </c>
       <c r="I66" t="n">
-        <v>157929.093831</v>
+        <v>158357.498336</v>
       </c>
       <c r="J66" t="n">
         <v>91477.36436199999</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>308.297551</v>
+        <v>308.033951</v>
       </c>
       <c r="F67" t="n">
-        <v>728.060087</v>
+        <v>726.401818</v>
       </c>
       <c r="G67" t="n">
-        <v>1498.964982</v>
+        <v>1491.611846</v>
       </c>
       <c r="H67" t="n">
-        <v>2628.895177</v>
+        <v>2601.286362</v>
       </c>
       <c r="I67" t="n">
-        <v>4467.543409</v>
+        <v>4345.54386</v>
       </c>
       <c r="J67" t="n">
         <v>50787.711404</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1017.743173</v>
+        <v>1017.083466</v>
       </c>
       <c r="F68" t="n">
-        <v>2313.803822</v>
+        <v>2309.797309</v>
       </c>
       <c r="G68" t="n">
-        <v>4602.387657</v>
+        <v>4585.141359</v>
       </c>
       <c r="H68" t="n">
-        <v>7538.804244</v>
+        <v>7478.661487</v>
       </c>
       <c r="I68" t="n">
-        <v>11439.092523</v>
+        <v>11204.954983</v>
       </c>
       <c r="J68" t="n">
         <v>86100.107911</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.147546</v>
+        <v>0.060115</v>
       </c>
       <c r="F69" t="n">
-        <v>0.78272</v>
+        <v>0.318988</v>
       </c>
       <c r="G69" t="n">
-        <v>2.779095</v>
+        <v>1.133084</v>
       </c>
       <c r="H69" t="n">
-        <v>8.309486</v>
+        <v>3.390959</v>
       </c>
       <c r="I69" t="n">
-        <v>29.646063</v>
+        <v>12.130856</v>
       </c>
       <c r="J69" t="n">
         <v>5392.864673</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>8213.500690999999</v>
+        <v>8214.609381</v>
       </c>
       <c r="F70" t="n">
-        <v>18174.046402</v>
+        <v>18180.146151</v>
       </c>
       <c r="G70" t="n">
-        <v>34297.888466</v>
+        <v>34320.751389</v>
       </c>
       <c r="H70" t="n">
-        <v>54920.62203</v>
+        <v>54994.055793</v>
       </c>
       <c r="I70" t="n">
-        <v>84364.117927</v>
+        <v>84646.048221</v>
       </c>
       <c r="J70" t="n">
         <v>32257.533703</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>24069.055607</v>
+        <v>24071.609704</v>
       </c>
       <c r="F71" t="n">
-        <v>55901.825349</v>
+        <v>55916.316059</v>
       </c>
       <c r="G71" t="n">
-        <v>100058.545198</v>
+        <v>100109.967588</v>
       </c>
       <c r="H71" t="n">
-        <v>146290.065437</v>
+        <v>146442.135057</v>
       </c>
       <c r="I71" t="n">
-        <v>205415.381598</v>
+        <v>205953.451854</v>
       </c>
       <c r="J71" t="n">
         <v>115384.102373</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>12645.336196</v>
+        <v>12646.333255</v>
       </c>
       <c r="F72" t="n">
-        <v>25445.596999</v>
+        <v>25450.524324</v>
       </c>
       <c r="G72" t="n">
-        <v>43690.385844</v>
+        <v>43706.873435</v>
       </c>
       <c r="H72" t="n">
-        <v>64371.839831</v>
+        <v>64419.723637</v>
       </c>
       <c r="I72" t="n">
-        <v>91893.953524</v>
+        <v>92060.986485</v>
       </c>
       <c r="J72" t="n">
         <v>77171.665303</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>24.801857</v>
+        <v>22.832301</v>
       </c>
       <c r="F73" t="n">
-        <v>47.205902</v>
+        <v>39.615604</v>
       </c>
       <c r="G73" t="n">
-        <v>74.306848</v>
+        <v>56.081291</v>
       </c>
       <c r="H73" t="n">
-        <v>120.544744</v>
+        <v>79.255895</v>
       </c>
       <c r="I73" t="n">
-        <v>274.929033</v>
+        <v>149.357862</v>
       </c>
       <c r="J73" t="n">
         <v>34575.304172</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.058225</v>
+        <v>0.023723</v>
       </c>
       <c r="F74" t="n">
-        <v>0.374111</v>
+        <v>0.152464</v>
       </c>
       <c r="G74" t="n">
-        <v>1.417426</v>
+        <v>0.577908</v>
       </c>
       <c r="H74" t="n">
-        <v>4.244264</v>
+        <v>1.732011</v>
       </c>
       <c r="I74" t="n">
-        <v>14.846231</v>
+        <v>6.074921</v>
       </c>
       <c r="J74" t="n">
         <v>2562.875049</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>7991.798469</v>
+        <v>7991.80689</v>
       </c>
       <c r="F75" t="n">
-        <v>8589.988445000001</v>
+        <v>8589.995983999999</v>
       </c>
       <c r="G75" t="n">
-        <v>12153.087992</v>
+        <v>12153.046018</v>
       </c>
       <c r="H75" t="n">
-        <v>17318.75246</v>
+        <v>17318.520151</v>
       </c>
       <c r="I75" t="n">
-        <v>22502.594335</v>
+        <v>22501.652032</v>
       </c>
       <c r="J75" t="n">
         <v>41680.313714</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6288.026923</v>
+        <v>6287.804046</v>
       </c>
       <c r="F76" t="n">
-        <v>6856.294337</v>
+        <v>6855.555765</v>
       </c>
       <c r="G76" t="n">
-        <v>7830.255948</v>
+        <v>7828.461181</v>
       </c>
       <c r="H76" t="n">
-        <v>9484.504365999999</v>
+        <v>9480.085064999999</v>
       </c>
       <c r="I76" t="n">
-        <v>11514.912802</v>
+        <v>11501.519738</v>
       </c>
       <c r="J76" t="n">
         <v>204168.641248</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>30570.561307</v>
+        <v>30570.651752</v>
       </c>
       <c r="F77" t="n">
-        <v>37272.075636</v>
+        <v>37272.315568</v>
       </c>
       <c r="G77" t="n">
-        <v>55129.603489</v>
+        <v>55130.126006</v>
       </c>
       <c r="H77" t="n">
-        <v>75999.104645</v>
+        <v>76000.287968</v>
       </c>
       <c r="I77" t="n">
-        <v>91381.361536</v>
+        <v>91384.693222</v>
       </c>
       <c r="J77" t="n">
         <v>60389.345617</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>34437.624628</v>
+        <v>34437.403128</v>
       </c>
       <c r="F78" t="n">
-        <v>31943.935474</v>
+        <v>31943.326027</v>
       </c>
       <c r="G78" t="n">
-        <v>37833.975575</v>
+        <v>37832.313252</v>
       </c>
       <c r="H78" t="n">
-        <v>48223.3132</v>
+        <v>48218.779089</v>
       </c>
       <c r="I78" t="n">
-        <v>60359.887177</v>
+        <v>60345.251807</v>
       </c>
       <c r="J78" t="n">
         <v>285017.712559</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>40138.357143</v>
+        <v>40138.507327</v>
       </c>
       <c r="F79" t="n">
-        <v>57044.341734</v>
+        <v>57044.851062</v>
       </c>
       <c r="G79" t="n">
-        <v>107132.596686</v>
+        <v>107134.235714</v>
       </c>
       <c r="H79" t="n">
-        <v>190161.024348</v>
+        <v>190166.30935</v>
       </c>
       <c r="I79" t="n">
-        <v>286023.892875</v>
+        <v>286042.879732</v>
       </c>
       <c r="J79" t="n">
         <v>95891.252053</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>799.25075</v>
+        <v>799.246299</v>
       </c>
       <c r="F80" t="n">
-        <v>747.566321</v>
+        <v>747.553902</v>
       </c>
       <c r="G80" t="n">
-        <v>948.657694</v>
+        <v>948.619539</v>
       </c>
       <c r="H80" t="n">
-        <v>1346.130619</v>
+        <v>1346.006711</v>
       </c>
       <c r="I80" t="n">
-        <v>1886.34389</v>
+        <v>1885.86505</v>
       </c>
       <c r="J80" t="n">
         <v>10737.088865</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>61473.08168</v>
+        <v>61473.317508</v>
       </c>
       <c r="F81" t="n">
-        <v>89321.164946</v>
+        <v>89321.990206</v>
       </c>
       <c r="G81" t="n">
-        <v>166905.604885</v>
+        <v>166908.296083</v>
       </c>
       <c r="H81" t="n">
-        <v>294142.965224</v>
+        <v>294151.72851</v>
       </c>
       <c r="I81" t="n">
-        <v>443526.968518</v>
+        <v>443558.851574</v>
       </c>
       <c r="J81" t="n">
         <v>111541.438303</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>11.574428</v>
+        <v>11.520252</v>
       </c>
       <c r="F82" t="n">
-        <v>14.082765</v>
+        <v>13.908477</v>
       </c>
       <c r="G82" t="n">
-        <v>23.541693</v>
+        <v>22.992795</v>
       </c>
       <c r="H82" t="n">
-        <v>46.417791</v>
+        <v>44.689602</v>
       </c>
       <c r="I82" t="n">
-        <v>113.360451</v>
+        <v>107.234168</v>
       </c>
       <c r="J82" t="n">
         <v>92355.72595199999</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>24680.659671</v>
+        <v>24680.677796</v>
       </c>
       <c r="F83" t="n">
-        <v>35923.324337</v>
+        <v>35923.277005</v>
       </c>
       <c r="G83" t="n">
-        <v>66592.993222</v>
+        <v>66592.22659799999</v>
       </c>
       <c r="H83" t="n">
-        <v>115669.748349</v>
+        <v>115665.554557</v>
       </c>
       <c r="I83" t="n">
-        <v>169725.22396</v>
+        <v>169706.598222</v>
       </c>
       <c r="J83" t="n">
         <v>517719.057465</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>28445.039363</v>
+        <v>28445.04469</v>
       </c>
       <c r="F86" t="n">
-        <v>35896.741581</v>
+        <v>35896.760279</v>
       </c>
       <c r="G86" t="n">
-        <v>53329.717407</v>
+        <v>53329.778553</v>
       </c>
       <c r="H86" t="n">
-        <v>85373.160708</v>
+        <v>85373.372603</v>
       </c>
       <c r="I86" t="n">
-        <v>121942.561317</v>
+        <v>121943.369401</v>
       </c>
       <c r="J86" t="n">
         <v>61708.241267</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1297.146537</v>
+        <v>1297.145633</v>
       </c>
       <c r="F87" t="n">
-        <v>1831.760979</v>
+        <v>1831.757051</v>
       </c>
       <c r="G87" t="n">
-        <v>3083.818024</v>
+        <v>3083.801907</v>
       </c>
       <c r="H87" t="n">
-        <v>5448.246683</v>
+        <v>5448.180924</v>
       </c>
       <c r="I87" t="n">
-        <v>8403.794062999999</v>
+        <v>8403.51275</v>
       </c>
       <c r="J87" t="n">
         <v>46253.823284</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>30591.217306</v>
+        <v>30591.212237</v>
       </c>
       <c r="F88" t="n">
-        <v>34590.916034</v>
+        <v>34590.904762</v>
       </c>
       <c r="G88" t="n">
-        <v>47292.302117</v>
+        <v>47292.279524</v>
       </c>
       <c r="H88" t="n">
-        <v>73350.17899099999</v>
+        <v>73350.123032</v>
       </c>
       <c r="I88" t="n">
-        <v>105416.832858</v>
+        <v>105416.645026</v>
       </c>
       <c r="J88" t="n">
         <v>158666.966135</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5064.97933</v>
+        <v>5064.979787</v>
       </c>
       <c r="F89" t="n">
-        <v>6083.771627</v>
+        <v>6083.773308</v>
       </c>
       <c r="G89" t="n">
-        <v>9004.150559</v>
+        <v>9004.156136</v>
       </c>
       <c r="H89" t="n">
-        <v>14470.960979</v>
+        <v>14470.980579</v>
       </c>
       <c r="I89" t="n">
-        <v>20801.604282</v>
+        <v>20801.680321</v>
       </c>
       <c r="J89" t="n">
         <v>17494.426856</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>10481.571297</v>
+        <v>10481.566804</v>
       </c>
       <c r="F90" t="n">
-        <v>12809.2642</v>
+        <v>12809.249039</v>
       </c>
       <c r="G90" t="n">
-        <v>19375.660809</v>
+        <v>19375.608107</v>
       </c>
       <c r="H90" t="n">
-        <v>31941.65696</v>
+        <v>31941.460181</v>
       </c>
       <c r="I90" t="n">
-        <v>46894.507022</v>
+        <v>46893.707119</v>
       </c>
       <c r="J90" t="n">
         <v>155561.414351</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5448.105501</v>
+        <v>5448.104855</v>
       </c>
       <c r="F91" t="n">
-        <v>6841.32743</v>
+        <v>6841.324949</v>
       </c>
       <c r="G91" t="n">
-        <v>10183.236948</v>
+        <v>10183.228202</v>
       </c>
       <c r="H91" t="n">
-        <v>16027.797743</v>
+        <v>16027.767843</v>
       </c>
       <c r="I91" t="n">
-        <v>22161.773258</v>
+        <v>22161.667711</v>
       </c>
       <c r="J91" t="n">
         <v>37524.597287</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>9015.416238</v>
+        <v>9015.417713000001</v>
       </c>
       <c r="F92" t="n">
-        <v>11425.406656</v>
+        <v>11425.411801</v>
       </c>
       <c r="G92" t="n">
-        <v>17606.034741</v>
+        <v>17606.051554</v>
       </c>
       <c r="H92" t="n">
-        <v>28570.916753</v>
+        <v>28570.974675</v>
       </c>
       <c r="I92" t="n">
-        <v>40524.079475</v>
+        <v>40524.298733</v>
       </c>
       <c r="J92" t="n">
         <v>25321.52339</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>331.141836</v>
+        <v>331.141372</v>
       </c>
       <c r="F93" t="n">
-        <v>439.704913</v>
+        <v>439.703087</v>
       </c>
       <c r="G93" t="n">
-        <v>712.5185719999999</v>
+        <v>712.511467</v>
       </c>
       <c r="H93" t="n">
-        <v>1246.405553</v>
+        <v>1246.376298</v>
       </c>
       <c r="I93" t="n">
-        <v>1923.010321</v>
+        <v>1922.881057</v>
       </c>
       <c r="J93" t="n">
         <v>19061.935436</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>73646.854035</v>
+        <v>73646.840276</v>
       </c>
       <c r="F94" t="n">
-        <v>98283.247171</v>
+        <v>98283.187525</v>
       </c>
       <c r="G94" t="n">
-        <v>150754.187173</v>
+        <v>150753.971224</v>
       </c>
       <c r="H94" t="n">
-        <v>244199.296169</v>
+        <v>244198.526114</v>
       </c>
       <c r="I94" t="n">
-        <v>348886.983913</v>
+        <v>348884.064065</v>
       </c>
       <c r="J94" t="n">
         <v>768738.6646</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>85072.12074499999</v>
+        <v>85072.13824099999</v>
       </c>
       <c r="F95" t="n">
-        <v>115627.106618</v>
+        <v>115627.171136</v>
       </c>
       <c r="G95" t="n">
-        <v>184497.597158</v>
+        <v>184497.816425</v>
       </c>
       <c r="H95" t="n">
-        <v>309494.383399</v>
+        <v>309495.15871</v>
       </c>
       <c r="I95" t="n">
-        <v>454031.914777</v>
+        <v>454034.894354</v>
       </c>
       <c r="J95" t="n">
         <v>238970.967172</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>19610.573648</v>
+        <v>19610.572993</v>
       </c>
       <c r="F96" t="n">
-        <v>23198.261481</v>
+        <v>23198.260697</v>
       </c>
       <c r="G96" t="n">
-        <v>31925.987706</v>
+        <v>31925.990458</v>
       </c>
       <c r="H96" t="n">
-        <v>49043.971484</v>
+        <v>49043.991111</v>
       </c>
       <c r="I96" t="n">
-        <v>69322.897125</v>
+        <v>69322.988769</v>
       </c>
       <c r="J96" t="n">
         <v>77382.57289</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>14139.734163</v>
+        <v>14139.735399</v>
       </c>
       <c r="F97" t="n">
-        <v>15443.920089</v>
+        <v>15443.925145</v>
       </c>
       <c r="G97" t="n">
-        <v>20633.834766</v>
+        <v>20633.852422</v>
       </c>
       <c r="H97" t="n">
-        <v>31609.12056</v>
+        <v>31609.183911</v>
       </c>
       <c r="I97" t="n">
-        <v>45235.717567</v>
+        <v>45235.966674</v>
       </c>
       <c r="J97" t="n">
         <v>29267.893312</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>157678.817436</v>
+        <v>157679.077946</v>
       </c>
       <c r="F98" t="n">
-        <v>233915.703431</v>
+        <v>233916.79438</v>
       </c>
       <c r="G98" t="n">
-        <v>275018.443735</v>
+        <v>275021.413926</v>
       </c>
       <c r="H98" t="n">
-        <v>330986.391682</v>
+        <v>330994.533022</v>
       </c>
       <c r="I98" t="n">
-        <v>397465.908193</v>
+        <v>397493.093714</v>
       </c>
       <c r="J98" t="n">
         <v>159632.815724</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>47897.310594</v>
+        <v>47897.167152</v>
       </c>
       <c r="F99" t="n">
-        <v>81951.220075</v>
+        <v>81950.531349</v>
       </c>
       <c r="G99" t="n">
-        <v>112833.919357</v>
+        <v>112831.785814</v>
       </c>
       <c r="H99" t="n">
-        <v>153613.88449</v>
+        <v>153607.508059</v>
       </c>
       <c r="I99" t="n">
-        <v>201068.35653</v>
+        <v>201045.971598</v>
       </c>
       <c r="J99" t="n">
         <v>493122.57964</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>62754.253788</v>
+        <v>62754.325605</v>
       </c>
       <c r="F100" t="n">
-        <v>92185.425003</v>
+        <v>92185.740718</v>
       </c>
       <c r="G100" t="n">
-        <v>110094.030113</v>
+        <v>110094.937901</v>
       </c>
       <c r="H100" t="n">
-        <v>135339.513463</v>
+        <v>135342.118125</v>
       </c>
       <c r="I100" t="n">
-        <v>165948.376153</v>
+        <v>165957.390523</v>
       </c>
       <c r="J100" t="n">
         <v>92819.663552</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>101161.247257</v>
+        <v>101161.438656</v>
       </c>
       <c r="F101" t="n">
-        <v>159650.599701</v>
+        <v>159651.425035</v>
       </c>
       <c r="G101" t="n">
-        <v>202216.267244</v>
+        <v>202218.6052</v>
       </c>
       <c r="H101" t="n">
-        <v>257856.20843</v>
+        <v>257862.841631</v>
       </c>
       <c r="I101" t="n">
-        <v>321995.062994</v>
+        <v>322017.782132</v>
       </c>
       <c r="J101" t="n">
         <v>126419.693579</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>305747.520626</v>
+        <v>305747.094795</v>
       </c>
       <c r="F102" t="n">
-        <v>511676.168623</v>
+        <v>511674.219628</v>
       </c>
       <c r="G102" t="n">
-        <v>694699.393112</v>
+        <v>694693.547354</v>
       </c>
       <c r="H102" t="n">
-        <v>943060.946627</v>
+        <v>943043.681745</v>
       </c>
       <c r="I102" t="n">
-        <v>1241080.691796</v>
+        <v>1241019.823652</v>
       </c>
       <c r="J102" t="n">
         <v>2207820.701475</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>625606.656535</v>
+        <v>625606.915078</v>
       </c>
       <c r="F103" t="n">
-        <v>894594.906356</v>
+        <v>894596.338417</v>
       </c>
       <c r="G103" t="n">
-        <v>1024498.728346</v>
+        <v>1024503.498378</v>
       </c>
       <c r="H103" t="n">
-        <v>1211290.954266</v>
+        <v>1211305.564127</v>
       </c>
       <c r="I103" t="n">
-        <v>1439406.003258</v>
+        <v>1439457.775722</v>
       </c>
       <c r="J103" t="n">
         <v>1058849.775947</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>49210.7075</v>
+        <v>49210.652625</v>
       </c>
       <c r="F104" t="n">
-        <v>79336.820358</v>
+        <v>79336.58163</v>
       </c>
       <c r="G104" t="n">
-        <v>103458.209813</v>
+        <v>103457.537592</v>
       </c>
       <c r="H104" t="n">
-        <v>137360.919996</v>
+        <v>137358.956105</v>
       </c>
       <c r="I104" t="n">
-        <v>178429.420952</v>
+        <v>178422.411509</v>
       </c>
       <c r="J104" t="n">
         <v>297238.377335</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>26406.863314</v>
+        <v>26406.833865</v>
       </c>
       <c r="F105" t="n">
-        <v>42937.86397</v>
+        <v>42937.748148</v>
       </c>
       <c r="G105" t="n">
-        <v>57092.778953</v>
+        <v>57092.470781</v>
       </c>
       <c r="H105" t="n">
-        <v>76077.599029</v>
+        <v>76076.787054</v>
       </c>
       <c r="I105" t="n">
-        <v>98449.518556</v>
+        <v>98446.96636799999</v>
       </c>
       <c r="J105" t="n">
         <v>144090.521235</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>360892.655607</v>
+        <v>360892.675125</v>
       </c>
       <c r="F106" t="n">
-        <v>607823.083141</v>
+        <v>607823.051335</v>
       </c>
       <c r="G106" t="n">
-        <v>838320.2334049999</v>
+        <v>838319.714915</v>
       </c>
       <c r="H106" t="n">
-        <v>1143244.943734</v>
+        <v>1143242.636819</v>
       </c>
       <c r="I106" t="n">
-        <v>1494841.265249</v>
+        <v>1494831.873723</v>
       </c>
       <c r="J106" t="n">
         <v>1910276.692852</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1427.705663</v>
+        <v>1427.643343</v>
       </c>
       <c r="F107" t="n">
-        <v>2535.760369</v>
+        <v>2535.457505</v>
       </c>
       <c r="G107" t="n">
-        <v>3436.373444</v>
+        <v>3435.49538</v>
       </c>
       <c r="H107" t="n">
-        <v>4626.865912</v>
+        <v>4624.363214</v>
       </c>
       <c r="I107" t="n">
-        <v>6096.463786</v>
+        <v>6087.791866</v>
       </c>
       <c r="J107" t="n">
         <v>105862.262938</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>45360.888859</v>
+        <v>45360.46927</v>
       </c>
       <c r="F108" t="n">
-        <v>72741.660441</v>
+        <v>72739.885431</v>
       </c>
       <c r="G108" t="n">
-        <v>92472.926341</v>
+        <v>92468.18797299999</v>
       </c>
       <c r="H108" t="n">
-        <v>118281.217079</v>
+        <v>118268.543138</v>
       </c>
       <c r="I108" t="n">
-        <v>148164.871388</v>
+        <v>148123.525358</v>
       </c>
       <c r="J108" t="n">
         <v>617169.006687</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>80763.260045</v>
+        <v>80763.397499</v>
       </c>
       <c r="F109" t="n">
-        <v>130830.669996</v>
+        <v>130831.269824</v>
       </c>
       <c r="G109" t="n">
-        <v>179101.785954</v>
+        <v>179103.555833</v>
       </c>
       <c r="H109" t="n">
-        <v>251511.680362</v>
+        <v>251516.964871</v>
       </c>
       <c r="I109" t="n">
-        <v>345505.91119</v>
+        <v>345524.926545</v>
       </c>
       <c r="J109" t="n">
         <v>219216.802516</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>339653.836341</v>
+        <v>339654.624072</v>
       </c>
       <c r="F110" t="n">
-        <v>578214.7006710001</v>
+        <v>578218.296004</v>
       </c>
       <c r="G110" t="n">
-        <v>795925.205811</v>
+        <v>795936.033585</v>
       </c>
       <c r="H110" t="n">
-        <v>1083161.316696</v>
+        <v>1083193.538577</v>
       </c>
       <c r="I110" t="n">
-        <v>1416009.72638</v>
+        <v>1416123.926218</v>
       </c>
       <c r="J110" t="n">
         <v>419494.946292</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>321735.67606</v>
+        <v>321735.790662</v>
       </c>
       <c r="F111" t="n">
-        <v>534276.62047</v>
+        <v>534277.107238</v>
       </c>
       <c r="G111" t="n">
-        <v>710032.6077169999</v>
+        <v>710034.054492</v>
       </c>
       <c r="H111" t="n">
-        <v>941684.595591</v>
+        <v>941689.031189</v>
       </c>
       <c r="I111" t="n">
-        <v>1216782.569666</v>
+        <v>1216798.903687</v>
       </c>
       <c r="J111" t="n">
         <v>1276460.071594</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>276267.300372</v>
+        <v>276266.594308</v>
       </c>
       <c r="F112" t="n">
-        <v>464586.878796</v>
+        <v>464583.634757</v>
       </c>
       <c r="G112" t="n">
-        <v>637634.139054</v>
+        <v>637624.203278</v>
       </c>
       <c r="H112" t="n">
-        <v>873969.302045</v>
+        <v>873939.271722</v>
       </c>
       <c r="I112" t="n">
-        <v>1158490.553311</v>
+        <v>1158382.536786</v>
       </c>
       <c r="J112" t="n">
         <v>2665043.218032</v>
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>980.466366</v>
+        <v>980.349037</v>
       </c>
       <c r="F113" t="n">
-        <v>1835.835225</v>
+        <v>1835.181485</v>
       </c>
       <c r="G113" t="n">
-        <v>3120.276067</v>
+        <v>3117.853346</v>
       </c>
       <c r="H113" t="n">
-        <v>5525.880993</v>
+        <v>5516.871709</v>
       </c>
       <c r="I113" t="n">
-        <v>8028.415294</v>
+        <v>7994.608022</v>
       </c>
       <c r="J113" t="n">
         <v>97001.17257</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1011.962204</v>
+        <v>1011.970279</v>
       </c>
       <c r="F114" t="n">
-        <v>2711.987476</v>
+        <v>2712.044322</v>
       </c>
       <c r="G114" t="n">
-        <v>7001.594261</v>
+        <v>7001.862219</v>
       </c>
       <c r="H114" t="n">
-        <v>16453.205838</v>
+        <v>16454.31</v>
       </c>
       <c r="I114" t="n">
-        <v>27504.870957</v>
+        <v>27508.985764</v>
       </c>
       <c r="J114" t="n">
         <v>28291.577565</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>25045.355429</v>
+        <v>25045.464684</v>
       </c>
       <c r="F115" t="n">
-        <v>54183.325869</v>
+        <v>54183.922763</v>
       </c>
       <c r="G115" t="n">
-        <v>116217.618392</v>
+        <v>116219.773156</v>
       </c>
       <c r="H115" t="n">
-        <v>244966.053589</v>
+        <v>244973.958711</v>
       </c>
       <c r="I115" t="n">
-        <v>392971.674169</v>
+        <v>393001.366635</v>
       </c>
       <c r="J115" t="n">
         <v>472063.066285</v>
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>20985.28716</v>
+        <v>20985.359759</v>
       </c>
       <c r="F116" t="n">
-        <v>25029.248332</v>
+        <v>25029.474914</v>
       </c>
       <c r="G116" t="n">
-        <v>35269.293388</v>
+        <v>35269.964851</v>
       </c>
       <c r="H116" t="n">
-        <v>47855.943765</v>
+        <v>47857.849058</v>
       </c>
       <c r="I116" t="n">
-        <v>58760.51281</v>
+        <v>58766.582719</v>
       </c>
       <c r="J116" t="n">
         <v>11736.027262</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>19761.125076</v>
+        <v>19761.150163</v>
       </c>
       <c r="F117" t="n">
-        <v>28098.435215</v>
+        <v>28098.515579</v>
       </c>
       <c r="G117" t="n">
-        <v>41989.740977</v>
+        <v>41989.978487</v>
       </c>
       <c r="H117" t="n">
-        <v>58017.045676</v>
+        <v>58017.715854</v>
       </c>
       <c r="I117" t="n">
-        <v>71263.730623</v>
+        <v>71265.850615</v>
       </c>
       <c r="J117" t="n">
         <v>62947.763077</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>26735.624362</v>
+        <v>26735.595858</v>
       </c>
       <c r="F118" t="n">
-        <v>30021.318105</v>
+        <v>30021.239403</v>
       </c>
       <c r="G118" t="n">
-        <v>39528.698209</v>
+        <v>39528.500474</v>
       </c>
       <c r="H118" t="n">
-        <v>50782.560353</v>
+        <v>50782.07587</v>
       </c>
       <c r="I118" t="n">
-        <v>59931.14845</v>
+        <v>59929.773334</v>
       </c>
       <c r="J118" t="n">
         <v>79727.390512</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>7223.168822</v>
+        <v>7223.169045</v>
       </c>
       <c r="F119" t="n">
-        <v>9822.787833</v>
+        <v>9822.784385000001</v>
       </c>
       <c r="G119" t="n">
-        <v>15412.660496</v>
+        <v>15412.638642</v>
       </c>
       <c r="H119" t="n">
-        <v>22682.380279</v>
+        <v>22682.291528</v>
       </c>
       <c r="I119" t="n">
-        <v>29526.828833</v>
+        <v>29526.486955</v>
       </c>
       <c r="J119" t="n">
         <v>39552.154627</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5307.802209</v>
+        <v>5307.813122</v>
       </c>
       <c r="F120" t="n">
-        <v>6383.842648</v>
+        <v>6383.876944</v>
       </c>
       <c r="G120" t="n">
-        <v>9090.076496</v>
+        <v>9090.179249000001</v>
       </c>
       <c r="H120" t="n">
-        <v>12488.430728</v>
+        <v>12488.726255</v>
       </c>
       <c r="I120" t="n">
-        <v>15554.208504</v>
+        <v>15555.164282</v>
       </c>
       <c r="J120" t="n">
         <v>9361.854938</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>36005.59066</v>
+        <v>36005.581388</v>
       </c>
       <c r="F121" t="n">
-        <v>48399.713967</v>
+        <v>48399.657446</v>
       </c>
       <c r="G121" t="n">
-        <v>75128.613461</v>
+        <v>75128.370692</v>
       </c>
       <c r="H121" t="n">
-        <v>108178.635308</v>
+        <v>108177.807727</v>
       </c>
       <c r="I121" t="n">
-        <v>136278.562667</v>
+        <v>136275.763165</v>
       </c>
       <c r="J121" t="n">
         <v>185769.752123</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>297820.332711</v>
+        <v>297820.261665</v>
       </c>
       <c r="F122" t="n">
-        <v>359788.92349</v>
+        <v>359788.720918</v>
       </c>
       <c r="G122" t="n">
-        <v>516220.451343</v>
+        <v>516219.901976</v>
       </c>
       <c r="H122" t="n">
-        <v>716472.42636</v>
+        <v>716470.956178</v>
       </c>
       <c r="I122" t="n">
-        <v>903707.064583</v>
+        <v>903702.4354</v>
       </c>
       <c r="J122" t="n">
         <v>1132362.61493</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>66895.545918</v>
+        <v>66959.873295</v>
       </c>
       <c r="F123" t="n">
-        <v>87331.55734299999</v>
+        <v>87526.04205600001</v>
       </c>
       <c r="G123" t="n">
-        <v>97565.25242999999</v>
+        <v>97963.495207</v>
       </c>
       <c r="H123" t="n">
-        <v>108605.43228</v>
+        <v>109415.188435</v>
       </c>
       <c r="I123" t="n">
-        <v>118979.959124</v>
+        <v>120924.167102</v>
       </c>
       <c r="J123" t="n">
         <v>38884.898266</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>499708.716845</v>
+        <v>499970.045136</v>
       </c>
       <c r="F124" t="n">
-        <v>647566.8270160001</v>
+        <v>648336.313861</v>
       </c>
       <c r="G124" t="n">
-        <v>709741.424011</v>
+        <v>711244.898453</v>
       </c>
       <c r="H124" t="n">
-        <v>777194.66873</v>
+        <v>780107.070684</v>
       </c>
       <c r="I124" t="n">
-        <v>848348.067987</v>
+        <v>854982.810451</v>
       </c>
       <c r="J124" t="n">
         <v>624005.688601</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>148819.517238</v>
+        <v>148493.86157</v>
       </c>
       <c r="F125" t="n">
-        <v>181613.087552</v>
+        <v>180649.115994</v>
       </c>
       <c r="G125" t="n">
-        <v>187961.767476</v>
+        <v>186060.050258</v>
       </c>
       <c r="H125" t="n">
-        <v>204207.387008</v>
+        <v>200485.228898</v>
       </c>
       <c r="I125" t="n">
-        <v>246867.388857</v>
+        <v>238288.438415</v>
       </c>
       <c r="J125" t="n">
         <v>675850.177901</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1090.717385</v>
+        <v>1090.674922</v>
       </c>
       <c r="F130" t="n">
-        <v>9631.810375999999</v>
+        <v>9630.657487</v>
       </c>
       <c r="G130" t="n">
-        <v>20100.763697</v>
+        <v>20094.596238</v>
       </c>
       <c r="H130" t="n">
-        <v>37062.008986</v>
+        <v>37031.615784</v>
       </c>
       <c r="I130" t="n">
-        <v>61139.744528</v>
+        <v>60960.64653</v>
       </c>
       <c r="J130" t="n">
         <v>2874723.481756</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.0019</v>
+        <v>0.0003</v>
       </c>
       <c r="F131" t="n">
-        <v>0.063127</v>
+        <v>0.009984</v>
       </c>
       <c r="G131" t="n">
-        <v>0.321315</v>
+        <v>0.050818</v>
       </c>
       <c r="H131" t="n">
-        <v>1.439668</v>
+        <v>0.227696</v>
       </c>
       <c r="I131" t="n">
-        <v>7.874306</v>
+        <v>1.245473</v>
       </c>
       <c r="J131" t="n">
         <v>100030.017903</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>51229.095517</v>
+        <v>51229.152127</v>
       </c>
       <c r="F132" t="n">
-        <v>410602.073133</v>
+        <v>410603.340955</v>
       </c>
       <c r="G132" t="n">
-        <v>753324.988245</v>
+        <v>753330.6940979999</v>
       </c>
       <c r="H132" t="n">
-        <v>1223848.33359</v>
+        <v>1223873.706342</v>
       </c>
       <c r="I132" t="n">
-        <v>1842467.398367</v>
+        <v>1842609.769792</v>
       </c>
       <c r="J132" t="n">
         <v>339152.35387</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>9308.203438</v>
+        <v>9308.214497999999</v>
       </c>
       <c r="F133" t="n">
-        <v>113151.510327</v>
+        <v>113151.861406</v>
       </c>
       <c r="G133" t="n">
-        <v>300553.691254</v>
+        <v>300555.752555</v>
       </c>
       <c r="H133" t="n">
-        <v>621106.927883</v>
+        <v>621117.78286</v>
       </c>
       <c r="I133" t="n">
-        <v>1047078.740138</v>
+        <v>1047145.978835</v>
       </c>
       <c r="J133" t="n">
         <v>399207.277433</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4342.410463</v>
+        <v>4342.410056</v>
       </c>
       <c r="F134" t="n">
-        <v>32236.925676</v>
+        <v>32236.933068</v>
       </c>
       <c r="G134" t="n">
-        <v>57014.975074</v>
+        <v>57015.083299</v>
       </c>
       <c r="H134" t="n">
-        <v>93048.95725000001</v>
+        <v>93049.723828</v>
       </c>
       <c r="I134" t="n">
-        <v>142682.389542</v>
+        <v>142687.794316</v>
       </c>
       <c r="J134" t="n">
         <v>104806.687135</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>643.6714899999999</v>
+        <v>643.6721680000001</v>
       </c>
       <c r="F135" t="n">
-        <v>6536.18685</v>
+        <v>6536.204725</v>
       </c>
       <c r="G135" t="n">
-        <v>15431.044794</v>
+        <v>15431.13884</v>
       </c>
       <c r="H135" t="n">
-        <v>30629.478069</v>
+        <v>30629.957513</v>
       </c>
       <c r="I135" t="n">
-        <v>52701.356949</v>
+        <v>52704.349019</v>
       </c>
       <c r="J135" t="n">
         <v>28677.21678</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>107.28962</v>
+        <v>107.28044</v>
       </c>
       <c r="F136" t="n">
-        <v>804.065755</v>
+        <v>803.895759</v>
       </c>
       <c r="G136" t="n">
-        <v>1318.906059</v>
+        <v>1318.394811</v>
       </c>
       <c r="H136" t="n">
-        <v>1934.868111</v>
+        <v>1933.421723</v>
       </c>
       <c r="I136" t="n">
-        <v>2753.647514</v>
+        <v>2747.731216</v>
       </c>
       <c r="J136" t="n">
         <v>79798.54158</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1795.129031</v>
+        <v>1795.130277</v>
       </c>
       <c r="F137" t="n">
-        <v>14800.338573</v>
+        <v>14800.364518</v>
       </c>
       <c r="G137" t="n">
-        <v>26976.048287</v>
+        <v>26976.167771</v>
       </c>
       <c r="H137" t="n">
-        <v>43536.263933</v>
+        <v>43536.833279</v>
       </c>
       <c r="I137" t="n">
-        <v>64703.255864</v>
+        <v>64706.589505</v>
       </c>
       <c r="J137" t="n">
         <v>35023.888685</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>14.305864</v>
+        <v>14.304151</v>
       </c>
       <c r="F138" t="n">
-        <v>114.230174</v>
+        <v>114.191225</v>
       </c>
       <c r="G138" t="n">
-        <v>210.708249</v>
+        <v>210.546127</v>
       </c>
       <c r="H138" t="n">
-        <v>339.174748</v>
+        <v>338.575043</v>
       </c>
       <c r="I138" t="n">
-        <v>493.657782</v>
+        <v>490.957167</v>
       </c>
       <c r="J138" t="n">
         <v>34380.866792</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.000348</v>
+        <v>5.5e-05</v>
       </c>
       <c r="F139" t="n">
-        <v>0.009239000000000001</v>
+        <v>0.001461</v>
       </c>
       <c r="G139" t="n">
-        <v>0.048794</v>
+        <v>0.007717</v>
       </c>
       <c r="H139" t="n">
-        <v>0.238965</v>
+        <v>0.037794</v>
       </c>
       <c r="I139" t="n">
-        <v>1.403386</v>
+        <v>0.221973</v>
       </c>
       <c r="J139" t="n">
         <v>18316.081346</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>164.512918</v>
+        <v>164.497018</v>
       </c>
       <c r="F140" t="n">
-        <v>1224.791577</v>
+        <v>1224.498046</v>
       </c>
       <c r="G140" t="n">
-        <v>2174.819479</v>
+        <v>2173.739888</v>
       </c>
       <c r="H140" t="n">
-        <v>3572.069363</v>
+        <v>3568.011696</v>
       </c>
       <c r="I140" t="n">
-        <v>5538.232302</v>
+        <v>5517.618229</v>
       </c>
       <c r="J140" t="n">
         <v>310641.456971</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1476.868411</v>
+        <v>1476.870019</v>
       </c>
       <c r="F141" t="n">
-        <v>13451.49388</v>
+        <v>13451.533449</v>
       </c>
       <c r="G141" t="n">
-        <v>28549.353012</v>
+        <v>28549.550773</v>
       </c>
       <c r="H141" t="n">
-        <v>52525.746562</v>
+        <v>52526.715825</v>
       </c>
       <c r="I141" t="n">
-        <v>86397.264167</v>
+        <v>86403.118166</v>
       </c>
       <c r="J141" t="n">
         <v>31095.067105</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>414.810615</v>
+        <v>414.810968</v>
       </c>
       <c r="F142" t="n">
-        <v>5591.331412</v>
+        <v>5591.338018</v>
       </c>
       <c r="G142" t="n">
-        <v>18389.549442</v>
+        <v>18389.494765</v>
       </c>
       <c r="H142" t="n">
-        <v>45846.567572</v>
+        <v>45845.465317</v>
       </c>
       <c r="I142" t="n">
-        <v>88604.62685499999</v>
+        <v>88593.571478</v>
       </c>
       <c r="J142" t="n">
         <v>332367.554344</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>102.64458</v>
+        <v>102.593138</v>
       </c>
       <c r="F146" t="n">
-        <v>107.695391</v>
+        <v>107.558036</v>
       </c>
       <c r="G146" t="n">
-        <v>118.061239</v>
+        <v>117.754434</v>
       </c>
       <c r="H146" t="n">
-        <v>148.786612</v>
+        <v>147.999315</v>
       </c>
       <c r="I146" t="n">
-        <v>206.151051</v>
+        <v>203.449829</v>
       </c>
       <c r="J146" t="n">
         <v>5831.111341</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1759.215636</v>
+        <v>1759.116199</v>
       </c>
       <c r="F147" t="n">
-        <v>2083.757887</v>
+        <v>2083.45109</v>
       </c>
       <c r="G147" t="n">
-        <v>2446.041387</v>
+        <v>2445.298558</v>
       </c>
       <c r="H147" t="n">
-        <v>3060.150108</v>
+        <v>3058.25079</v>
       </c>
       <c r="I147" t="n">
-        <v>4004.285866</v>
+        <v>3997.969772</v>
       </c>
       <c r="J147" t="n">
         <v>17497.637499</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>273606.773584</v>
+        <v>273606.924464</v>
       </c>
       <c r="F148" t="n">
-        <v>344206.550273</v>
+        <v>344206.994425</v>
       </c>
       <c r="G148" t="n">
-        <v>440323.078574</v>
+        <v>440324.128208</v>
       </c>
       <c r="H148" t="n">
-        <v>587689.797481</v>
+        <v>587692.484095</v>
       </c>
       <c r="I148" t="n">
-        <v>778468.685283</v>
+        <v>778477.702599</v>
       </c>
       <c r="J148" t="n">
         <v>959369.56936</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>9148.129228</v>
+        <v>9147.786355</v>
       </c>
       <c r="F149" t="n">
-        <v>10867.264879</v>
+        <v>10866.242741</v>
       </c>
       <c r="G149" t="n">
-        <v>14499.46733</v>
+        <v>14496.696873</v>
       </c>
       <c r="H149" t="n">
-        <v>19789.58636</v>
+        <v>19781.853424</v>
       </c>
       <c r="I149" t="n">
-        <v>27212.873672</v>
+        <v>27185.808873</v>
       </c>
       <c r="J149" t="n">
         <v>119628.357253</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>111883.621951</v>
+        <v>111882.719744</v>
       </c>
       <c r="F150" t="n">
-        <v>129333.399254</v>
+        <v>129330.827441</v>
       </c>
       <c r="G150" t="n">
-        <v>168414.834902</v>
+        <v>168407.846922</v>
       </c>
       <c r="H150" t="n">
-        <v>219525.110142</v>
+        <v>219505.611943</v>
       </c>
       <c r="I150" t="n">
-        <v>278480.872755</v>
+        <v>278414.738841</v>
       </c>
       <c r="J150" t="n">
         <v>527402.335248</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>46423.046832</v>
+        <v>46422.578068</v>
       </c>
       <c r="F151" t="n">
-        <v>57979.963629</v>
+        <v>57978.493783</v>
       </c>
       <c r="G151" t="n">
-        <v>80720.110728</v>
+        <v>80715.82429400001</v>
       </c>
       <c r="H151" t="n">
-        <v>110194.444206</v>
+        <v>110181.999158</v>
       </c>
       <c r="I151" t="n">
-        <v>144105.189908</v>
+        <v>144062.145946</v>
       </c>
       <c r="J151" t="n">
         <v>310365.458448</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>86798.436929</v>
+        <v>86796.66033300001</v>
       </c>
       <c r="F152" t="n">
-        <v>109161.761216</v>
+        <v>109156.106187</v>
       </c>
       <c r="G152" t="n">
-        <v>144944.877705</v>
+        <v>144929.48133</v>
       </c>
       <c r="H152" t="n">
-        <v>187528.486403</v>
+        <v>187487.413711</v>
       </c>
       <c r="I152" t="n">
-        <v>234804.536286</v>
+        <v>234672.712246</v>
       </c>
       <c r="J152" t="n">
         <v>644564.511445</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>189669.622813</v>
+        <v>189672.877171</v>
       </c>
       <c r="F153" t="n">
-        <v>228466.858635</v>
+        <v>228476.835075</v>
       </c>
       <c r="G153" t="n">
-        <v>318372.683038</v>
+        <v>318400.279403</v>
       </c>
       <c r="H153" t="n">
-        <v>451475.268018</v>
+        <v>451551.789127</v>
       </c>
       <c r="I153" t="n">
-        <v>625538.0416530001</v>
+        <v>625794.877849</v>
       </c>
       <c r="J153" t="n">
         <v>83176.125351</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>43521.702246</v>
+        <v>43521.938328</v>
       </c>
       <c r="F154" t="n">
-        <v>53599.511446</v>
+        <v>53600.253833</v>
       </c>
       <c r="G154" t="n">
-        <v>69959.702058</v>
+        <v>69961.54693900001</v>
       </c>
       <c r="H154" t="n">
-        <v>88136.440032</v>
+        <v>88140.667797</v>
       </c>
       <c r="I154" t="n">
-        <v>106227.273886</v>
+        <v>106238.504406</v>
       </c>
       <c r="J154" t="n">
         <v>96180.190415</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>50352.676035</v>
+        <v>50359.261568</v>
       </c>
       <c r="F155" t="n">
-        <v>92705.276144</v>
+        <v>92736.11098100001</v>
       </c>
       <c r="G155" t="n">
-        <v>237623.252463</v>
+        <v>237783.290406</v>
       </c>
       <c r="H155" t="n">
-        <v>447569.888073</v>
+        <v>448177.607638</v>
       </c>
       <c r="I155" t="n">
-        <v>740877.390457</v>
+        <v>743393.030935</v>
       </c>
       <c r="J155" t="n">
         <v>150249.714389</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>3656.263177</v>
+        <v>3648.653727</v>
       </c>
       <c r="F156" t="n">
-        <v>6562.879951</v>
+        <v>6527.614619</v>
       </c>
       <c r="G156" t="n">
-        <v>16433.588016</v>
+        <v>16252.490411</v>
       </c>
       <c r="H156" t="n">
-        <v>30393.769657</v>
+        <v>29714.435171</v>
       </c>
       <c r="I156" t="n">
-        <v>51355.426154</v>
+        <v>48583.53229</v>
       </c>
       <c r="J156" t="n">
         <v>1122458.41252</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1127.959652</v>
+        <v>1127.914728</v>
       </c>
       <c r="F157" t="n">
-        <v>2475.077392</v>
+        <v>2474.755489</v>
       </c>
       <c r="G157" t="n">
-        <v>6902.170092</v>
+        <v>6900.052735</v>
       </c>
       <c r="H157" t="n">
-        <v>12850.807383</v>
+        <v>12842.115249</v>
       </c>
       <c r="I157" t="n">
-        <v>19901.954424</v>
+        <v>19866.013823</v>
       </c>
       <c r="J157" t="n">
         <v>40972.347884</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>26741.220175</v>
+        <v>26741.467769</v>
       </c>
       <c r="F158" t="n">
-        <v>40791.233113</v>
+        <v>40792.343587</v>
       </c>
       <c r="G158" t="n">
-        <v>86305.44553500001</v>
+        <v>86310.709126</v>
       </c>
       <c r="H158" t="n">
-        <v>138723.058815</v>
+        <v>138739.194718</v>
       </c>
       <c r="I158" t="n">
-        <v>203861.40057</v>
+        <v>203905.763041</v>
       </c>
       <c r="J158" t="n">
         <v>271559.55833</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>480.624171</v>
+        <v>480.623158</v>
       </c>
       <c r="F159" t="n">
-        <v>804.11973</v>
+        <v>804.114776</v>
       </c>
       <c r="G159" t="n">
-        <v>1887.862542</v>
+        <v>1887.828611</v>
       </c>
       <c r="H159" t="n">
-        <v>3235.751991</v>
+        <v>3235.571564</v>
       </c>
       <c r="I159" t="n">
-        <v>4862.355469</v>
+        <v>4861.300484</v>
       </c>
       <c r="J159" t="n">
         <v>7090.187687</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>14448.911789</v>
+        <v>14449.73405</v>
       </c>
       <c r="F160" t="n">
-        <v>25703.916689</v>
+        <v>25707.563567</v>
       </c>
       <c r="G160" t="n">
-        <v>64357.485152</v>
+        <v>64375.432512</v>
       </c>
       <c r="H160" t="n">
-        <v>120272.524881</v>
+        <v>120336.87646</v>
       </c>
       <c r="I160" t="n">
-        <v>201632.086728</v>
+        <v>201880.973227</v>
       </c>
       <c r="J160" t="n">
         <v>221279.94999</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>7.094582</v>
+        <v>7.013417</v>
       </c>
       <c r="F162" t="n">
-        <v>5.546685</v>
+        <v>5.413604</v>
       </c>
       <c r="G162" t="n">
-        <v>7.504846</v>
+        <v>7.201723</v>
       </c>
       <c r="H162" t="n">
-        <v>11.025106</v>
+        <v>10.277341</v>
       </c>
       <c r="I162" t="n">
-        <v>19.392243</v>
+        <v>16.972674</v>
       </c>
       <c r="J162" t="n">
         <v>9312.743848</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1026.502712</v>
+        <v>1026.507288</v>
       </c>
       <c r="F163" t="n">
-        <v>1256.460821</v>
+        <v>1256.469811</v>
       </c>
       <c r="G163" t="n">
-        <v>2608.585473</v>
+        <v>2608.601488</v>
       </c>
       <c r="H163" t="n">
-        <v>4751.793179</v>
+        <v>4751.797999</v>
       </c>
       <c r="I163" t="n">
-        <v>7495.581599</v>
+        <v>7495.476415</v>
       </c>
       <c r="J163" t="n">
         <v>11008.510108</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>7128.908892</v>
+        <v>7128.947081</v>
       </c>
       <c r="F164" t="n">
-        <v>9840.21437</v>
+        <v>9840.300106999999</v>
       </c>
       <c r="G164" t="n">
-        <v>22177.884289</v>
+        <v>22178.067487</v>
       </c>
       <c r="H164" t="n">
-        <v>43667.168235</v>
+        <v>43667.273694</v>
       </c>
       <c r="I164" t="n">
-        <v>74538.888767</v>
+        <v>74537.394048</v>
       </c>
       <c r="J164" t="n">
         <v>124277.385803</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>47884.862232</v>
+        <v>47885.429545</v>
       </c>
       <c r="F165" t="n">
-        <v>58376.06317</v>
+        <v>58377.713753</v>
       </c>
       <c r="G165" t="n">
-        <v>105165.531212</v>
+        <v>105171.388898</v>
       </c>
       <c r="H165" t="n">
-        <v>174393.23254</v>
+        <v>174413.035853</v>
       </c>
       <c r="I165" t="n">
-        <v>265500.646263</v>
+        <v>265579.120087</v>
       </c>
       <c r="J165" t="n">
         <v>32431.167847</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>32770.895638</v>
+        <v>32771.225521</v>
       </c>
       <c r="F166" t="n">
-        <v>36978.780886</v>
+        <v>36979.647144</v>
       </c>
       <c r="G166" t="n">
-        <v>68149.82298700001</v>
+        <v>68152.883713</v>
       </c>
       <c r="H166" t="n">
-        <v>115010.720952</v>
+        <v>115021.049793</v>
       </c>
       <c r="I166" t="n">
-        <v>173805.791551</v>
+        <v>173845.999209</v>
       </c>
       <c r="J166" t="n">
         <v>68402.88118500001</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>50977.003601</v>
+        <v>50976.554754</v>
       </c>
       <c r="F167" t="n">
-        <v>54604.848835</v>
+        <v>54603.458567</v>
       </c>
       <c r="G167" t="n">
-        <v>97415.378319</v>
+        <v>97409.779839</v>
       </c>
       <c r="H167" t="n">
-        <v>164850.195007</v>
+        <v>164829.27901</v>
       </c>
       <c r="I167" t="n">
-        <v>256486.363673</v>
+        <v>256398.335299</v>
       </c>
       <c r="J167" t="n">
         <v>750888.78939</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>313.15601</v>
+        <v>313.156214</v>
       </c>
       <c r="F168" t="n">
-        <v>372.723588</v>
+        <v>372.722686</v>
       </c>
       <c r="G168" t="n">
-        <v>723.348437</v>
+        <v>723.3399010000001</v>
       </c>
       <c r="H168" t="n">
-        <v>1286.753641</v>
+        <v>1286.710429</v>
       </c>
       <c r="I168" t="n">
-        <v>2053.173627</v>
+        <v>2052.967608</v>
       </c>
       <c r="J168" t="n">
         <v>3928.937363</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>71413.84176</v>
+        <v>71414.233805</v>
       </c>
       <c r="F169" t="n">
-        <v>84604.876516</v>
+        <v>84605.80240499999</v>
       </c>
       <c r="G169" t="n">
-        <v>163506.17957</v>
+        <v>163509.067815</v>
       </c>
       <c r="H169" t="n">
-        <v>299456.822957</v>
+        <v>299465.572105</v>
       </c>
       <c r="I169" t="n">
-        <v>501800.779922</v>
+        <v>501831.915452</v>
       </c>
       <c r="J169" t="n">
         <v>641342.305621</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>8707.687625</v>
+        <v>8707.751523000001</v>
       </c>
       <c r="F170" t="n">
-        <v>12353.304454</v>
+        <v>12353.486322</v>
       </c>
       <c r="G170" t="n">
-        <v>27299.050576</v>
+        <v>27299.697329</v>
       </c>
       <c r="H170" t="n">
-        <v>52005.890198</v>
+        <v>52008.029505</v>
       </c>
       <c r="I170" t="n">
-        <v>85584.43823299999</v>
+        <v>85592.77297000001</v>
       </c>
       <c r="J170" t="n">
         <v>87905.827065</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>34193.477112</v>
+        <v>34193.564259</v>
       </c>
       <c r="F171" t="n">
-        <v>38713.376936</v>
+        <v>38713.48477</v>
       </c>
       <c r="G171" t="n">
-        <v>71653.968681</v>
+        <v>71653.94154499999</v>
       </c>
       <c r="H171" t="n">
-        <v>121656.465116</v>
+        <v>121655.402426</v>
       </c>
       <c r="I171" t="n">
-        <v>185125.72403</v>
+        <v>185119.505732</v>
       </c>
       <c r="J171" t="n">
         <v>284522.331706</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3152.691958</v>
+        <v>3151.003633</v>
       </c>
       <c r="F172" t="n">
-        <v>3321.711941</v>
+        <v>3317.052346</v>
       </c>
       <c r="G172" t="n">
-        <v>5497.109236</v>
+        <v>5481.361073</v>
       </c>
       <c r="H172" t="n">
-        <v>8429.583252</v>
+        <v>8380.954113</v>
       </c>
       <c r="I172" t="n">
-        <v>12234.038693</v>
+        <v>12059.363561</v>
       </c>
       <c r="J172" t="n">
         <v>702095.260887</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>691.544912</v>
+        <v>691.55142</v>
       </c>
       <c r="F173" t="n">
-        <v>971.8635849999999</v>
+        <v>971.883955</v>
       </c>
       <c r="G173" t="n">
-        <v>2136.746061</v>
+        <v>2136.827958</v>
       </c>
       <c r="H173" t="n">
-        <v>4057.495781</v>
+        <v>4057.796819</v>
       </c>
       <c r="I173" t="n">
-        <v>6749.0944</v>
+        <v>6750.357675</v>
       </c>
       <c r="J173" t="n">
         <v>4313.848895</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>47818.109803</v>
+        <v>47817.101121</v>
       </c>
       <c r="F174" t="n">
-        <v>51604.96319</v>
+        <v>51601.879753</v>
       </c>
       <c r="G174" t="n">
-        <v>91546.678051</v>
+        <v>91534.50074800001</v>
       </c>
       <c r="H174" t="n">
-        <v>151795.949442</v>
+        <v>151751.77601</v>
       </c>
       <c r="I174" t="n">
-        <v>229644.325902</v>
+        <v>229464.436364</v>
       </c>
       <c r="J174" t="n">
         <v>1112469.938408</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1433.489865</v>
+        <v>1433.505626</v>
       </c>
       <c r="F175" t="n">
-        <v>2376.929274</v>
+        <v>2376.989218</v>
       </c>
       <c r="G175" t="n">
-        <v>6163.71957</v>
+        <v>6164.010322</v>
       </c>
       <c r="H175" t="n">
-        <v>13522.124253</v>
+        <v>13523.364755</v>
       </c>
       <c r="I175" t="n">
-        <v>25186.4322</v>
+        <v>25192.222905</v>
       </c>
       <c r="J175" t="n">
         <v>12517.395834</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>122.444814</v>
+        <v>122.444172</v>
       </c>
       <c r="F176" t="n">
-        <v>124.200186</v>
+        <v>124.198177</v>
       </c>
       <c r="G176" t="n">
-        <v>213.328002</v>
+        <v>213.319717</v>
       </c>
       <c r="H176" t="n">
-        <v>346.46609</v>
+        <v>346.435272</v>
       </c>
       <c r="I176" t="n">
-        <v>515.543664</v>
+        <v>515.416887</v>
       </c>
       <c r="J176" t="n">
         <v>1241.435691</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>191958.650306</v>
+        <v>191960.373983</v>
       </c>
       <c r="F177" t="n">
-        <v>278775.024229</v>
+        <v>278780.394089</v>
       </c>
       <c r="G177" t="n">
-        <v>620226.6391349999</v>
+        <v>620247.528102</v>
       </c>
       <c r="H177" t="n">
-        <v>1161082.229058</v>
+        <v>1161155.342854</v>
       </c>
       <c r="I177" t="n">
-        <v>1835963.888514</v>
+        <v>1836252.648148</v>
       </c>
       <c r="J177" t="n">
         <v>1309846.740004</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>307.008422</v>
+        <v>307.007407</v>
       </c>
       <c r="F178" t="n">
-        <v>387.59001</v>
+        <v>387.58453</v>
       </c>
       <c r="G178" t="n">
-        <v>773.313583</v>
+        <v>773.284145</v>
       </c>
       <c r="H178" t="n">
-        <v>1388.03197</v>
+        <v>1387.906763</v>
       </c>
       <c r="I178" t="n">
-        <v>2217.889614</v>
+        <v>2217.336116</v>
       </c>
       <c r="J178" t="n">
         <v>5695.161941</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>212.729754</v>
+        <v>212.72923</v>
       </c>
       <c r="F179" t="n">
-        <v>235.731624</v>
+        <v>235.729064</v>
       </c>
       <c r="G179" t="n">
-        <v>438.429772</v>
+        <v>438.415997</v>
       </c>
       <c r="H179" t="n">
-        <v>741.829025</v>
+        <v>741.771058</v>
       </c>
       <c r="I179" t="n">
-        <v>1114.312904</v>
+        <v>1114.064649</v>
       </c>
       <c r="J179" t="n">
         <v>2630.544204</v>
@@ -14130,19 +14130,19 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1.2e-05</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
         <v>5e-06</v>
       </c>
       <c r="G181" t="n">
-        <v>3e-06</v>
+        <v>-7e-06</v>
       </c>
       <c r="H181" t="n">
-        <v>-6e-06</v>
+        <v>8e-06</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="J181" t="n">
         <v>1e-06</v>
